--- a/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="281">
   <si>
     <t>year</t>
   </si>
@@ -37,6 +37,822 @@
   </si>
   <si>
     <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -103,25 +919,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -129,7 +945,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>5943366</v>
@@ -150,7 +966,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>5943366</v>
@@ -171,7 +987,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>5943366</v>
@@ -192,7 +1008,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>5943366</v>
@@ -213,7 +1029,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>5943366</v>
@@ -234,7 +1050,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>5943366</v>
@@ -255,7 +1071,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>5943366</v>
@@ -276,7 +1092,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>5943366</v>
@@ -297,7 +1113,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>5943366</v>
@@ -318,7 +1134,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>5943366</v>
@@ -347,25 +1163,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -373,7 +1189,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="C2">
         <v>6068249</v>
@@ -394,7 +1210,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>165</v>
       </c>
       <c r="C3">
         <v>6068249</v>
@@ -415,7 +1231,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="C4">
         <v>6068249</v>
@@ -436,7 +1252,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>6068249</v>
@@ -457,7 +1273,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="C6">
         <v>6068249</v>
@@ -478,7 +1294,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="C7">
         <v>6068249</v>
@@ -499,7 +1315,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="C8">
         <v>6068249</v>
@@ -520,7 +1336,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="C9">
         <v>6068249</v>
@@ -541,7 +1357,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="C10">
         <v>6068249</v>
@@ -562,7 +1378,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="C11">
         <v>6068249</v>
@@ -591,25 +1407,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>194</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
@@ -617,7 +1433,7 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="C2">
         <v>6113975</v>
@@ -638,7 +1454,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="C3">
         <v>6113975</v>
@@ -659,7 +1475,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C4">
         <v>6113975</v>
@@ -680,7 +1496,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>6113975</v>
@@ -701,7 +1517,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="C6">
         <v>6113975</v>
@@ -722,7 +1538,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="C7">
         <v>6113975</v>
@@ -743,7 +1559,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="C8">
         <v>6113975</v>
@@ -764,7 +1580,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="C9">
         <v>6113975</v>
@@ -785,7 +1601,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="C10">
         <v>6113975</v>
@@ -806,7 +1622,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="C11">
         <v>6113975</v>
@@ -835,25 +1651,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
@@ -861,7 +1677,7 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="C2">
         <v>6138839</v>
@@ -882,7 +1698,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="C3">
         <v>6138839</v>
@@ -903,7 +1719,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C4">
         <v>6138839</v>
@@ -924,7 +1740,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="C5">
         <v>6138839</v>
@@ -945,7 +1761,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
       <c r="C6">
         <v>6138839</v>
@@ -966,7 +1782,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="C7">
         <v>6138839</v>
@@ -987,7 +1803,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="C8">
         <v>6138839</v>
@@ -1008,7 +1824,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>205</v>
       </c>
       <c r="C9">
         <v>6138839</v>
@@ -1029,7 +1845,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>206</v>
       </c>
       <c r="C10">
         <v>6138839</v>
@@ -1050,7 +1866,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="C11">
         <v>6138839</v>
@@ -1079,25 +1895,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>226</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>227</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>228</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2">
@@ -1105,7 +1921,7 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>215</v>
       </c>
       <c r="C2">
         <v>6162955</v>
@@ -1126,7 +1942,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="C3">
         <v>6162955</v>
@@ -1147,7 +1963,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="C4">
         <v>6162955</v>
@@ -1168,7 +1984,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="C5">
         <v>6162955</v>
@@ -1189,7 +2005,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>219</v>
       </c>
       <c r="C6">
         <v>6162955</v>
@@ -1210,7 +2026,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="C7">
         <v>6162955</v>
@@ -1231,7 +2047,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>221</v>
       </c>
       <c r="C8">
         <v>6162955</v>
@@ -1252,7 +2068,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>222</v>
       </c>
       <c r="C9">
         <v>6162955</v>
@@ -1273,7 +2089,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>223</v>
       </c>
       <c r="C10">
         <v>6162955</v>
@@ -1294,7 +2110,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>224</v>
       </c>
       <c r="C11">
         <v>6162955</v>
@@ -1323,25 +2139,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>242</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>244</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -1349,7 +2165,7 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="C2">
         <v>6183676</v>
@@ -1370,7 +2186,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>233</v>
       </c>
       <c r="C3">
         <v>6183676</v>
@@ -1391,7 +2207,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>234</v>
       </c>
       <c r="C4">
         <v>6183676</v>
@@ -1412,7 +2228,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>235</v>
       </c>
       <c r="C5">
         <v>6183676</v>
@@ -1433,7 +2249,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C6">
         <v>6183676</v>
@@ -1454,7 +2270,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>237</v>
       </c>
       <c r="C7">
         <v>6183676</v>
@@ -1475,7 +2291,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>238</v>
       </c>
       <c r="C8">
         <v>6183676</v>
@@ -1496,7 +2312,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>239</v>
       </c>
       <c r="C9">
         <v>6183676</v>
@@ -1517,7 +2333,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="C10">
         <v>6183676</v>
@@ -1538,7 +2354,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="C11">
         <v>6183676</v>
@@ -1567,25 +2383,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>261</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
@@ -1593,7 +2409,7 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="C2">
         <v>6200800</v>
@@ -1614,7 +2430,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="C3">
         <v>6200800</v>
@@ -1635,7 +2451,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="C4">
         <v>6200800</v>
@@ -1656,7 +2472,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6200800</v>
@@ -1677,7 +2493,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>253</v>
       </c>
       <c r="C6">
         <v>6200800</v>
@@ -1698,7 +2514,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="C7">
         <v>6200800</v>
@@ -1719,7 +2535,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="C8">
         <v>6200800</v>
@@ -1740,7 +2556,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>6200800</v>
@@ -1761,7 +2577,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="C10">
         <v>6200800</v>
@@ -1782,7 +2598,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>258</v>
       </c>
       <c r="C11">
         <v>6200800</v>
@@ -1811,25 +2627,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -1837,7 +2653,7 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6213533</v>
@@ -1858,7 +2674,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="C3">
         <v>6213533</v>
@@ -1879,7 +2695,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="C4">
         <v>6213533</v>
@@ -1900,7 +2716,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="C5">
         <v>6213533</v>
@@ -1921,7 +2737,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>270</v>
       </c>
       <c r="C6">
         <v>6213533</v>
@@ -1942,7 +2758,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="C7">
         <v>6213533</v>
@@ -1963,7 +2779,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <v>6213533</v>
@@ -1984,7 +2800,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="C9">
         <v>6213533</v>
@@ -2005,7 +2821,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="C10">
         <v>6213533</v>
@@ -2026,7 +2842,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6213533</v>
@@ -2055,25 +2871,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -2081,7 +2897,7 @@
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>5968060</v>
@@ -2102,7 +2918,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>5968060</v>
@@ -2123,7 +2939,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>5968060</v>
@@ -2144,7 +2960,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>5968060</v>
@@ -2165,7 +2981,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>5968060</v>
@@ -2186,7 +3002,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>5968060</v>
@@ -2207,7 +3023,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>5968060</v>
@@ -2228,7 +3044,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>5968060</v>
@@ -2249,7 +3065,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>5968060</v>
@@ -2270,7 +3086,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>5968060</v>
@@ -2299,25 +3115,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -2325,7 +3141,7 @@
         <v>2002</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>5986631</v>
@@ -2346,7 +3162,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>5986631</v>
@@ -2367,7 +3183,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>5986631</v>
@@ -2388,7 +3204,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>5986631</v>
@@ -2409,7 +3225,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>5986631</v>
@@ -2430,7 +3246,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C7">
         <v>5986631</v>
@@ -2451,7 +3267,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>5986631</v>
@@ -2472,7 +3288,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>5986631</v>
@@ -2493,7 +3309,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>5986631</v>
@@ -2514,7 +3330,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>5986631</v>
@@ -2543,25 +3359,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
@@ -2569,7 +3385,7 @@
         <v>2003</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>5998599</v>
@@ -2590,7 +3406,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>5998599</v>
@@ -2611,7 +3427,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>5998599</v>
@@ -2632,7 +3448,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>5998599</v>
@@ -2653,7 +3469,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>5998599</v>
@@ -2674,7 +3490,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>5998599</v>
@@ -2695,7 +3511,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>5998599</v>
@@ -2716,7 +3532,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>5998599</v>
@@ -2737,7 +3553,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>5998599</v>
@@ -2758,7 +3574,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C11">
         <v>5998599</v>
@@ -2787,25 +3603,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
@@ -2813,7 +3629,7 @@
         <v>2004</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>6004671</v>
@@ -2834,7 +3650,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>6004671</v>
@@ -2855,7 +3671,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C4">
         <v>6004671</v>
@@ -2876,7 +3692,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>6004671</v>
@@ -2897,7 +3713,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>6004671</v>
@@ -2918,7 +3734,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>6004671</v>
@@ -2939,7 +3755,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C8">
         <v>6004671</v>
@@ -2960,7 +3776,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>6004671</v>
@@ -2981,7 +3797,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <v>6004671</v>
@@ -3002,7 +3818,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>6004671</v>
@@ -3031,25 +3847,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
@@ -3057,7 +3873,7 @@
         <v>2005</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="C2">
         <v>6005578</v>
@@ -3078,7 +3894,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>6005578</v>
@@ -3099,7 +3915,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="C4">
         <v>6005578</v>
@@ -3120,7 +3936,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="C5">
         <v>6005578</v>
@@ -3141,7 +3957,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>6005578</v>
@@ -3162,7 +3978,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C7">
         <v>6005578</v>
@@ -3183,7 +3999,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C8">
         <v>6005578</v>
@@ -3204,7 +4020,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C9">
         <v>6005578</v>
@@ -3225,7 +4041,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C10">
         <v>6005578</v>
@@ -3246,7 +4062,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C11">
         <v>6005578</v>
@@ -3275,25 +4091,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
@@ -3301,7 +4117,7 @@
         <v>2006</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="C2">
         <v>6002319</v>
@@ -3322,7 +4138,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>6002319</v>
@@ -3343,7 +4159,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>6002319</v>
@@ -3364,7 +4180,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C5">
         <v>6002319</v>
@@ -3385,7 +4201,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="C6">
         <v>6002319</v>
@@ -3406,7 +4222,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="C7">
         <v>6002319</v>
@@ -3427,7 +4243,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="C8">
         <v>6002319</v>
@@ -3448,7 +4264,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C9">
         <v>6002319</v>
@@ -3469,7 +4285,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="C10">
         <v>6002319</v>
@@ -3490,7 +4306,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="C11">
         <v>6002319</v>
@@ -3519,25 +4335,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2">
@@ -3545,7 +4361,7 @@
         <v>2007</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="C2">
         <v>6009824</v>
@@ -3566,7 +4382,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="C3">
         <v>6009824</v>
@@ -3587,7 +4403,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <v>6009824</v>
@@ -3608,7 +4424,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="C5">
         <v>6009824</v>
@@ -3629,7 +4445,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>6009824</v>
@@ -3650,7 +4466,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C7">
         <v>6009824</v>
@@ -3671,7 +4487,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="C8">
         <v>6009824</v>
@@ -3692,7 +4508,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C9">
         <v>6009824</v>
@@ -3713,7 +4529,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="C10">
         <v>6009824</v>
@@ -3734,7 +4550,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="C11">
         <v>6009824</v>
@@ -3763,25 +4579,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
@@ -3789,7 +4605,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="C2">
         <v>6048279</v>
@@ -3810,7 +4626,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>6048279</v>
@@ -3831,7 +4647,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="C4">
         <v>6048279</v>
@@ -3852,7 +4668,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>6048279</v>
@@ -3873,7 +4689,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="C6">
         <v>6048279</v>
@@ -3894,7 +4710,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C7">
         <v>6048279</v>
@@ -3915,7 +4731,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="C8">
         <v>6048279</v>
@@ -3936,7 +4752,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="C9">
         <v>6048279</v>
@@ -3957,7 +4773,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="C10">
         <v>6048279</v>
@@ -3978,7 +4794,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="C11">
         <v>6048279</v>

--- a/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="281">
   <si>
     <t>year</t>
   </si>
@@ -919,25 +919,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>25</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -945,7 +945,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>5943366</v>
@@ -966,7 +966,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>5943366</v>
@@ -987,7 +987,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>5943366</v>
@@ -1008,7 +1008,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>5943366</v>
@@ -1029,7 +1029,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>5943366</v>
@@ -1050,7 +1050,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>5943366</v>
@@ -1071,7 +1071,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>5943366</v>
@@ -1092,7 +1092,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>5943366</v>
@@ -1113,7 +1113,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>5943366</v>
@@ -1134,7 +1134,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>5943366</v>
@@ -1163,25 +1163,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>175</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>176</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>177</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>178</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -1189,7 +1189,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6068249</v>
@@ -1210,7 +1210,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6068249</v>
@@ -1231,7 +1231,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6068249</v>
@@ -1252,7 +1252,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6068249</v>
@@ -1273,7 +1273,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6068249</v>
@@ -1294,7 +1294,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6068249</v>
@@ -1315,7 +1315,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6068249</v>
@@ -1336,7 +1336,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6068249</v>
@@ -1357,7 +1357,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6068249</v>
@@ -1378,7 +1378,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6068249</v>
@@ -1407,25 +1407,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>192</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>195</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -1433,7 +1433,7 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6113975</v>
@@ -1454,7 +1454,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6113975</v>
@@ -1475,7 +1475,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6113975</v>
@@ -1496,7 +1496,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6113975</v>
@@ -1517,7 +1517,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6113975</v>
@@ -1538,7 +1538,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6113975</v>
@@ -1559,7 +1559,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6113975</v>
@@ -1580,7 +1580,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6113975</v>
@@ -1601,7 +1601,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6113975</v>
@@ -1622,7 +1622,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6113975</v>
@@ -1651,25 +1651,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -1677,7 +1677,7 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6138839</v>
@@ -1698,7 +1698,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6138839</v>
@@ -1719,7 +1719,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6138839</v>
@@ -1740,7 +1740,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6138839</v>
@@ -1761,7 +1761,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6138839</v>
@@ -1782,7 +1782,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6138839</v>
@@ -1803,7 +1803,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6138839</v>
@@ -1824,7 +1824,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6138839</v>
@@ -1845,7 +1845,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6138839</v>
@@ -1866,7 +1866,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6138839</v>
@@ -1895,25 +1895,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -1921,7 +1921,7 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6162955</v>
@@ -1942,7 +1942,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6162955</v>
@@ -1963,7 +1963,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6162955</v>
@@ -1984,7 +1984,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6162955</v>
@@ -2005,7 +2005,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6162955</v>
@@ -2026,7 +2026,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6162955</v>
@@ -2047,7 +2047,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6162955</v>
@@ -2068,7 +2068,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6162955</v>
@@ -2089,7 +2089,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6162955</v>
@@ -2110,7 +2110,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6162955</v>
@@ -2139,25 +2139,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -2165,7 +2165,7 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6183676</v>
@@ -2186,7 +2186,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6183676</v>
@@ -2207,7 +2207,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6183676</v>
@@ -2228,7 +2228,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6183676</v>
@@ -2249,7 +2249,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6183676</v>
@@ -2270,7 +2270,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6183676</v>
@@ -2291,7 +2291,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6183676</v>
@@ -2312,7 +2312,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6183676</v>
@@ -2333,7 +2333,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6183676</v>
@@ -2354,7 +2354,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6183676</v>
@@ -2383,25 +2383,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -2409,7 +2409,7 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6200800</v>
@@ -2430,7 +2430,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6200800</v>
@@ -2451,7 +2451,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6200800</v>
@@ -2472,7 +2472,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6200800</v>
@@ -2493,7 +2493,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6200800</v>
@@ -2514,7 +2514,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6200800</v>
@@ -2535,7 +2535,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6200800</v>
@@ -2556,7 +2556,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6200800</v>
@@ -2577,7 +2577,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6200800</v>
@@ -2598,7 +2598,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6200800</v>
@@ -2674,7 +2674,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6213533</v>
@@ -2695,7 +2695,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6213533</v>
@@ -2716,7 +2716,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6213533</v>
@@ -2737,7 +2737,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6213533</v>
@@ -2758,7 +2758,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6213533</v>
@@ -2779,7 +2779,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6213533</v>
@@ -2800,7 +2800,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6213533</v>
@@ -2821,7 +2821,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6213533</v>
@@ -2871,25 +2871,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -2897,7 +2897,7 @@
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>5968060</v>
@@ -2918,7 +2918,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>5968060</v>
@@ -2939,7 +2939,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>5968060</v>
@@ -2960,7 +2960,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>5968060</v>
@@ -2981,7 +2981,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>5968060</v>
@@ -3002,7 +3002,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>5968060</v>
@@ -3023,7 +3023,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>5968060</v>
@@ -3044,7 +3044,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>5968060</v>
@@ -3065,7 +3065,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>5968060</v>
@@ -3086,7 +3086,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>5968060</v>
@@ -3115,25 +3115,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3141,7 +3141,7 @@
         <v>2002</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>5986631</v>
@@ -3162,7 +3162,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>5986631</v>
@@ -3183,7 +3183,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>5986631</v>
@@ -3204,7 +3204,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>5986631</v>
@@ -3225,7 +3225,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>5986631</v>
@@ -3246,7 +3246,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>5986631</v>
@@ -3267,7 +3267,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>5986631</v>
@@ -3288,7 +3288,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>5986631</v>
@@ -3309,7 +3309,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>5986631</v>
@@ -3330,7 +3330,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>5986631</v>
@@ -3359,25 +3359,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3385,7 +3385,7 @@
         <v>2003</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>5998599</v>
@@ -3406,7 +3406,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>5998599</v>
@@ -3427,7 +3427,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>5998599</v>
@@ -3448,7 +3448,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>5998599</v>
@@ -3469,7 +3469,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>5998599</v>
@@ -3490,7 +3490,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>5998599</v>
@@ -3511,7 +3511,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>5998599</v>
@@ -3532,7 +3532,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>5998599</v>
@@ -3553,7 +3553,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>5998599</v>
@@ -3574,7 +3574,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>5998599</v>
@@ -3603,25 +3603,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3629,7 +3629,7 @@
         <v>2004</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6004671</v>
@@ -3650,7 +3650,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6004671</v>
@@ -3671,7 +3671,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6004671</v>
@@ -3692,7 +3692,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6004671</v>
@@ -3713,7 +3713,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6004671</v>
@@ -3734,7 +3734,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6004671</v>
@@ -3755,7 +3755,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6004671</v>
@@ -3776,7 +3776,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6004671</v>
@@ -3797,7 +3797,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6004671</v>
@@ -3818,7 +3818,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6004671</v>
@@ -3847,25 +3847,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>110</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3873,7 +3873,7 @@
         <v>2005</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6005578</v>
@@ -3894,7 +3894,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6005578</v>
@@ -3915,7 +3915,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6005578</v>
@@ -3936,7 +3936,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6005578</v>
@@ -3957,7 +3957,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6005578</v>
@@ -3978,7 +3978,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6005578</v>
@@ -3999,7 +3999,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6005578</v>
@@ -4020,7 +4020,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6005578</v>
@@ -4041,7 +4041,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6005578</v>
@@ -4062,7 +4062,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6005578</v>
@@ -4091,25 +4091,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>126</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -4117,7 +4117,7 @@
         <v>2006</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6002319</v>
@@ -4138,7 +4138,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6002319</v>
@@ -4159,7 +4159,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6002319</v>
@@ -4180,7 +4180,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6002319</v>
@@ -4201,7 +4201,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6002319</v>
@@ -4222,7 +4222,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6002319</v>
@@ -4243,7 +4243,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6002319</v>
@@ -4264,7 +4264,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6002319</v>
@@ -4285,7 +4285,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6002319</v>
@@ -4306,7 +4306,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6002319</v>
@@ -4335,25 +4335,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>143</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>144</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -4361,7 +4361,7 @@
         <v>2007</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6009824</v>
@@ -4382,7 +4382,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6009824</v>
@@ -4403,7 +4403,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6009824</v>
@@ -4424,7 +4424,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6009824</v>
@@ -4445,7 +4445,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6009824</v>
@@ -4466,7 +4466,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6009824</v>
@@ -4487,7 +4487,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6009824</v>
@@ -4508,7 +4508,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6009824</v>
@@ -4529,7 +4529,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6009824</v>
@@ -4550,7 +4550,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6009824</v>
@@ -4579,25 +4579,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s">
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -4605,7 +4605,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>266</v>
       </c>
       <c r="C2">
         <v>6048279</v>
@@ -4626,7 +4626,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>275</v>
       </c>
       <c r="C3">
         <v>6048279</v>
@@ -4647,7 +4647,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>275</v>
       </c>
       <c r="C4">
         <v>6048279</v>
@@ -4668,7 +4668,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="C5">
         <v>6048279</v>
@@ -4689,7 +4689,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6048279</v>
@@ -4710,7 +4710,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>6048279</v>
@@ -4731,7 +4731,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>6048279</v>
@@ -4752,7 +4752,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>275</v>
       </c>
       <c r="C9">
         <v>6048279</v>
@@ -4773,7 +4773,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>275</v>
       </c>
       <c r="C10">
         <v>6048279</v>
@@ -4794,7 +4794,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>6048279</v>

--- a/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/total-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="281">
   <si>
     <t>year</t>
   </si>
